--- a/cet4/result/32_重生女帝_女王归来权谋路/32_重生女帝_女王归来权谋路_学习版.xlsx
+++ b/cet4/result/32_重生女帝_女王归来权谋路/32_重生女帝_女王归来权谋路_学习版.xlsx
@@ -397,1109 +397,647 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D45"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>January</v>
       </c>
       <c r="B2" t="str">
-        <v>January</v>
+        <v>/ˈdʒænjueri/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>一月</v>
       </c>
-      <c r="D2" t="str">
-        <v>January(一月)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>ceiling</v>
       </c>
       <c r="B3" t="str">
-        <v>ceiling</v>
+        <v>/ˈsiːlɪŋ/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>天花板</v>
       </c>
-      <c r="D3" t="str">
-        <v>ceiling(天花板)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>dark</v>
       </c>
       <c r="B4" t="str">
-        <v>dark</v>
+        <v>/dɑːrk/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>黑暗</v>
       </c>
-      <c r="D4" t="str">
-        <v>dark(黑暗)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>abroad</v>
       </c>
       <c r="B5" t="str">
-        <v>abroad</v>
+        <v>/əˈbrɔːd/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D5" t="str">
         <v>在国外</v>
       </c>
-      <c r="D5" t="str">
-        <v>abroad(在国外)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>background</v>
       </c>
       <c r="B6" t="str">
-        <v>background</v>
+        <v>/ˈbækɡraʊnd/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>背景</v>
       </c>
-      <c r="D6" t="str">
-        <v>background(背景)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>governor</v>
       </c>
       <c r="B7" t="str">
-        <v>governor</v>
+        <v>/ˈɡʌvərnər/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>统治者</v>
       </c>
-      <c r="D7" t="str">
-        <v>governor(统治者)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>crown</v>
       </c>
       <c r="B8" t="str">
-        <v>crown</v>
+        <v>/kraʊn/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D8" t="str">
         <v>王冠</v>
       </c>
-      <c r="D8" t="str">
-        <v>crown(王冠)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>university</v>
       </c>
       <c r="B9" t="str">
-        <v>university</v>
+        <v>/ˌjuːnɪˈvɜːrsəti/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>大学</v>
       </c>
-      <c r="D9" t="str">
-        <v>university(大学)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>numerous</v>
       </c>
       <c r="B10" t="str">
-        <v>numerous</v>
+        <v>/ˈnuːmərəs/</v>
       </c>
       <c r="C10" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>许多的</v>
       </c>
-      <c r="D10" t="str">
-        <v>numerous(许多的)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>poetry</v>
       </c>
       <c r="B11" t="str">
-        <v>poetry</v>
+        <v>/ˈpoʊətri/</v>
       </c>
       <c r="C11" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>诗歌</v>
       </c>
-      <c r="D11" t="str">
-        <v>poetry(诗歌)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>govern</v>
       </c>
       <c r="B12" t="str">
-        <v>govern</v>
+        <v>/ˈɡʌvərn/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D12" t="str">
         <v>统治</v>
       </c>
-      <c r="D12" t="str">
-        <v>govern(统治)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>fashionable</v>
       </c>
       <c r="B13" t="str">
-        <v>fashionable</v>
+        <v>/ˈfæʃnəbl/</v>
       </c>
       <c r="C13" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D13" t="str">
         <v>时髦的</v>
       </c>
-      <c r="D13" t="str">
-        <v>fashionable(时髦的)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>tobacco</v>
       </c>
       <c r="B14" t="str">
-        <v>tobacco</v>
+        <v>/təˈbækoʊ/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>烟草</v>
       </c>
-      <c r="D14" t="str">
-        <v>tobacco(烟草)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>seaman</v>
       </c>
       <c r="B15" t="str">
-        <v>seaman</v>
+        <v>/ˈsiːmən/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>海员</v>
       </c>
-      <c r="D15" t="str">
-        <v>seaman(海员)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>policeman</v>
       </c>
       <c r="B16" t="str">
-        <v>policeman</v>
+        <v>/pəˈliːsmən/</v>
       </c>
       <c r="C16" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>警察</v>
       </c>
-      <c r="D16" t="str">
-        <v>policeman(警察)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>wild</v>
       </c>
       <c r="B17" t="str">
-        <v>wild</v>
+        <v>/waɪld/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D17" t="str">
         <v>野生的</v>
       </c>
-      <c r="D17" t="str">
-        <v>wild(野生的)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>lonely</v>
       </c>
       <c r="B18" t="str">
-        <v>lonely</v>
+        <v>/ˈloʊnli/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D18" t="str">
         <v>寂寞的</v>
       </c>
-      <c r="D18" t="str">
-        <v>lonely(寂寞的)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>mouse</v>
       </c>
       <c r="B19" t="str">
-        <v>mouse</v>
+        <v>/maʊs/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D19" t="str">
         <v>鼠标</v>
       </c>
-      <c r="D19" t="str">
-        <v>mouse(鼠标)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>ocean</v>
       </c>
       <c r="B20" t="str">
-        <v>ocean</v>
+        <v>/ˈoʊʃn/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>海洋</v>
       </c>
-      <c r="D20" t="str">
-        <v>ocean(海洋)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>globe</v>
       </c>
       <c r="B21" t="str">
-        <v>globe</v>
+        <v>/ɡloʊb/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D21" t="str">
         <v>地球仪</v>
       </c>
-      <c r="D21" t="str">
-        <v>globe(地球仪)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>right</v>
       </c>
       <c r="B22" t="str">
-        <v>right</v>
+        <v>/raɪt/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./vt./vi./v./adj./adv.</v>
+      </c>
+      <c r="D22" t="str">
         <v>权利</v>
       </c>
-      <c r="D22" t="str">
-        <v>right(权利)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>honourable</v>
       </c>
       <c r="B23" t="str">
-        <v>honourable</v>
+        <v>/ˈɑːnərəbl/</v>
       </c>
       <c r="C23" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D23" t="str">
         <v>值得尊敬的</v>
       </c>
-      <c r="D23" t="str">
-        <v>honourable(值得尊敬的)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>accurate</v>
       </c>
       <c r="B24" t="str">
-        <v>accurate</v>
+        <v>/ˈækjərət/</v>
       </c>
       <c r="C24" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D24" t="str">
         <v>精确的</v>
       </c>
-      <c r="D24" t="str">
-        <v>accurate(精确的)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>punishment</v>
       </c>
       <c r="B25" t="str">
-        <v>punishment</v>
+        <v>/ˈpʌnɪʃmənt/</v>
       </c>
       <c r="C25" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>惩罚</v>
       </c>
-      <c r="D25" t="str">
-        <v>punishment(惩罚)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>skilled</v>
       </c>
       <c r="B26" t="str">
-        <v>skilled</v>
+        <v>/skɪld/</v>
       </c>
       <c r="C26" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D26" t="str">
         <v>熟练的</v>
       </c>
-      <c r="D26" t="str">
-        <v>skilled(熟练的)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>vocabulary</v>
       </c>
       <c r="B27" t="str">
-        <v>vocabulary</v>
+        <v>/vəˈkæbjəleri/</v>
       </c>
       <c r="C27" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>词汇</v>
       </c>
-      <c r="D27" t="str">
-        <v>vocabulary(词汇)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>circulate</v>
       </c>
       <c r="B28" t="str">
-        <v>circulate</v>
+        <v>/ˈsɜːrkjəleɪt/</v>
       </c>
       <c r="C28" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D28" t="str">
         <v>传播</v>
       </c>
-      <c r="D28" t="str">
-        <v>circulate(传播)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>network</v>
       </c>
       <c r="B29" t="str">
-        <v>network</v>
+        <v>/ˈnetwɜːrk/</v>
       </c>
       <c r="C29" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>网络</v>
       </c>
-      <c r="D29" t="str">
-        <v>network(网络)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>system</v>
       </c>
       <c r="B30" t="str">
-        <v>numerous</v>
+        <v>/ˈsɪstəm/</v>
       </c>
       <c r="C30" t="str">
-        <v>许多的</v>
+        <v>n.</v>
       </c>
       <c r="D30" t="str">
-        <v>numerous(许多的)📢</v>
+        <v>制度</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>branch</v>
       </c>
       <c r="B31" t="str">
-        <v>system</v>
+        <v>/bræntʃ/</v>
       </c>
       <c r="C31" t="str">
-        <v>制度</v>
+        <v>n./v.</v>
       </c>
       <c r="D31" t="str">
-        <v>system(制度)📢</v>
+        <v>分支</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>once</v>
       </c>
       <c r="B32" t="str">
-        <v>branch</v>
+        <v>/wʌns/</v>
       </c>
       <c r="C32" t="str">
-        <v>分支</v>
+        <v>n./v./adv./conj.</v>
       </c>
       <c r="D32" t="str">
-        <v>branch(分支)📢</v>
+        <v>曾经</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>illustrate</v>
       </c>
       <c r="B33" t="str">
-        <v>once</v>
+        <v>/ˈɪləstreɪt/</v>
       </c>
       <c r="C33" t="str">
-        <v>曾经</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>once(曾经)📢</v>
+        <v>说明</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>navy</v>
       </c>
       <c r="B34" t="str">
-        <v>network</v>
+        <v>/ˈneɪvi/</v>
       </c>
       <c r="C34" t="str">
-        <v>网络</v>
+        <v>n.</v>
       </c>
       <c r="D34" t="str">
-        <v>network(网络)📢</v>
+        <v>海军</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>labour</v>
       </c>
       <c r="B35" t="str">
-        <v>system</v>
+        <v>/ˈleɪbər/</v>
       </c>
       <c r="C35" t="str">
-        <v>系统</v>
+        <v>n./vi.</v>
       </c>
       <c r="D35" t="str">
-        <v>system(系统)📢</v>
+        <v>劳动力</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>weave</v>
       </c>
       <c r="B36" t="str">
-        <v>illustrate</v>
+        <v>/wiːv/</v>
       </c>
       <c r="C36" t="str">
-        <v>说明</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D36" t="str">
-        <v>illustrate(说明)📢</v>
+        <v>编织</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>suggest</v>
       </c>
       <c r="B37" t="str">
-        <v>punishment</v>
+        <v>/səˈdʒest,səɡˈdʒest/</v>
       </c>
       <c r="C37" t="str">
-        <v>惩罚</v>
+        <v>vt.</v>
       </c>
       <c r="D37" t="str">
-        <v>punishment(惩罚)📢</v>
+        <v>建议</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>neglect</v>
       </c>
       <c r="B38" t="str">
-        <v>honourable</v>
+        <v>/nɪˈɡlekt/</v>
       </c>
       <c r="C38" t="str">
-        <v>正直的</v>
+        <v>n./v.</v>
       </c>
       <c r="D38" t="str">
-        <v>honourable(正直的)📢</v>
+        <v>忽视</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>dance</v>
       </c>
       <c r="B39" t="str">
-        <v>navy</v>
+        <v>/dæns/</v>
       </c>
       <c r="C39" t="str">
-        <v>海军</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D39" t="str">
-        <v>navy(海军)📢</v>
+        <v>舞蹈</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>friendship</v>
       </c>
       <c r="B40" t="str">
-        <v>labour</v>
+        <v>/ˈfrendʃɪp/</v>
       </c>
       <c r="C40" t="str">
-        <v>劳动力</v>
+        <v>n.</v>
       </c>
       <c r="D40" t="str">
-        <v>labour(劳动力)📢</v>
+        <v>友谊</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>influence</v>
       </c>
       <c r="B41" t="str">
-        <v>weave</v>
+        <v>/ˈɪnfluəns/</v>
       </c>
       <c r="C41" t="str">
-        <v>编织</v>
+        <v>n./vt.</v>
       </c>
       <c r="D41" t="str">
-        <v>weave(编织)📢</v>
+        <v>影响力</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>interference</v>
       </c>
       <c r="B42" t="str">
-        <v>skilled</v>
+        <v>/ˌɪntərˈfɪrəns/</v>
       </c>
       <c r="C42" t="str">
-        <v>熟练的</v>
+        <v>n.</v>
       </c>
       <c r="D42" t="str">
-        <v>skilled(熟练的)📢</v>
+        <v>干扰</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>confuse</v>
       </c>
       <c r="B43" t="str">
-        <v>suggest</v>
+        <v>/kənˈfjuːz/</v>
       </c>
       <c r="C43" t="str">
-        <v>建议</v>
+        <v>vt.</v>
       </c>
       <c r="D43" t="str">
-        <v>suggest(建议)📢</v>
+        <v>使困惑</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>rein</v>
       </c>
       <c r="B44" t="str">
-        <v>right</v>
+        <v>/reɪn/</v>
       </c>
       <c r="C44" t="str">
-        <v>权利</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D44" t="str">
-        <v>right(权利)📢</v>
+        <v>缰绳</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>acceleration</v>
       </c>
       <c r="B45" t="str">
-        <v>illustrate</v>
+        <v>/əkˌseləˈreɪʃn/</v>
       </c>
       <c r="C45" t="str">
-        <v>举例说明</v>
+        <v>n.</v>
       </c>
       <c r="D45" t="str">
-        <v>illustrate(举例说明)📢</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>punishment</v>
-      </c>
-      <c r="C46" t="str">
-        <v>惩罚</v>
-      </c>
-      <c r="D46" t="str">
-        <v>punishment(惩罚)📢</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>neglect</v>
-      </c>
-      <c r="C47" t="str">
-        <v>忽视</v>
-      </c>
-      <c r="D47" t="str">
-        <v>neglect(忽视)📢</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>suggest</v>
-      </c>
-      <c r="C48" t="str">
-        <v>暗示</v>
-      </c>
-      <c r="D48" t="str">
-        <v>suggest(暗示)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>honourable</v>
-      </c>
-      <c r="C49" t="str">
-        <v>荣誉的</v>
-      </c>
-      <c r="D49" t="str">
-        <v>honourable(荣誉的)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>dark</v>
-      </c>
-      <c r="C50" t="str">
-        <v>黑暗</v>
-      </c>
-      <c r="D50" t="str">
-        <v>dark(黑暗)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>accurate</v>
-      </c>
-      <c r="C51" t="str">
-        <v>精确的</v>
-      </c>
-      <c r="D51" t="str">
-        <v>accurate(精确的)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>right</v>
-      </c>
-      <c r="C52" t="str">
-        <v>权利</v>
-      </c>
-      <c r="D52" t="str">
-        <v>right(权利)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>crown</v>
-      </c>
-      <c r="C53" t="str">
-        <v>王冠</v>
-      </c>
-      <c r="D53" t="str">
-        <v>crown(王冠)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>honourable</v>
-      </c>
-      <c r="C54" t="str">
-        <v>正直的</v>
-      </c>
-      <c r="D54" t="str">
-        <v>honourable(正直的)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>govern</v>
-      </c>
-      <c r="C55" t="str">
-        <v>统治</v>
-      </c>
-      <c r="D55" t="str">
-        <v>govern(统治)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>system</v>
-      </c>
-      <c r="C56" t="str">
-        <v>制度</v>
-      </c>
-      <c r="D56" t="str">
-        <v>system(制度)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>right</v>
-      </c>
-      <c r="C57" t="str">
-        <v>权利</v>
-      </c>
-      <c r="D57" t="str">
-        <v>right(权利)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>university</v>
-      </c>
-      <c r="C58" t="str">
-        <v>大学</v>
-      </c>
-      <c r="D58" t="str">
-        <v>university(大学)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>branch</v>
-      </c>
-      <c r="C59" t="str">
-        <v>分支</v>
-      </c>
-      <c r="D59" t="str">
-        <v>branch(分支)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>network</v>
-      </c>
-      <c r="C60" t="str">
-        <v>网络</v>
-      </c>
-      <c r="D60" t="str">
-        <v>network(网络)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>poetry</v>
-      </c>
-      <c r="C61" t="str">
-        <v>诗歌</v>
-      </c>
-      <c r="D61" t="str">
-        <v>poetry(诗歌)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>dance</v>
-      </c>
-      <c r="C62" t="str">
-        <v>舞蹈</v>
-      </c>
-      <c r="D62" t="str">
-        <v>dance(舞蹈)📢</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>friendship</v>
-      </c>
-      <c r="C63" t="str">
-        <v>友谊</v>
-      </c>
-      <c r="D63" t="str">
-        <v>friendship(友谊)📢</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>influence</v>
-      </c>
-      <c r="C64" t="str">
-        <v>影响力</v>
-      </c>
-      <c r="D64" t="str">
-        <v>influence(影响力)📢</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>circulate</v>
-      </c>
-      <c r="C65" t="str">
-        <v>传播</v>
-      </c>
-      <c r="D65" t="str">
-        <v>circulate(传播)📢</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
-        <v>interference</v>
-      </c>
-      <c r="C66" t="str">
-        <v>干扰</v>
-      </c>
-      <c r="D66" t="str">
-        <v>interference(干扰)📢</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="str">
-        <v>confuse</v>
-      </c>
-      <c r="C67" t="str">
-        <v>使困惑</v>
-      </c>
-      <c r="D67" t="str">
-        <v>confuse(使困惑)📢</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="str">
-        <v>university</v>
-      </c>
-      <c r="C68" t="str">
-        <v>大学</v>
-      </c>
-      <c r="D68" t="str">
-        <v>university(大学)📢</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="str">
-        <v>skilled</v>
-      </c>
-      <c r="C69" t="str">
-        <v>有技能的</v>
-      </c>
-      <c r="D69" t="str">
-        <v>skilled(有技能的)📢</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" t="str">
-        <v>system</v>
-      </c>
-      <c r="C70" t="str">
-        <v>系统</v>
-      </c>
-      <c r="D70" t="str">
-        <v>system(系统)📢</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71" t="str">
-        <v>lonely</v>
-      </c>
-      <c r="C71" t="str">
-        <v>寂寞的</v>
-      </c>
-      <c r="D71" t="str">
-        <v>lonely(寂寞的)📢</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" t="str">
-        <v>honourable</v>
-      </c>
-      <c r="C72" t="str">
-        <v>值得尊敬的</v>
-      </c>
-      <c r="D72" t="str">
-        <v>honourable(值得尊敬的)📢</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" t="str">
-        <v>rein</v>
-      </c>
-      <c r="C73" t="str">
-        <v>缰绳</v>
-      </c>
-      <c r="D73" t="str">
-        <v>rein(缰绳)📢</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74" t="str">
-        <v>govern</v>
-      </c>
-      <c r="C74" t="str">
-        <v>统治</v>
-      </c>
-      <c r="D74" t="str">
-        <v>govern(统治)📢</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75">
-        <v>74</v>
-      </c>
-      <c r="B75" t="str">
-        <v>honourable</v>
-      </c>
-      <c r="C75" t="str">
-        <v>正直的</v>
-      </c>
-      <c r="D75" t="str">
-        <v>honourable(正直的)📢</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76" t="str">
-        <v>vocabulary</v>
-      </c>
-      <c r="C76" t="str">
-        <v>词汇</v>
-      </c>
-      <c r="D76" t="str">
-        <v>vocabulary(词汇)📢</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77">
-        <v>76</v>
-      </c>
-      <c r="B77" t="str">
-        <v>once</v>
-      </c>
-      <c r="C77" t="str">
-        <v>曾经</v>
-      </c>
-      <c r="D77" t="str">
-        <v>once(曾经)📢</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78">
-        <v>77</v>
-      </c>
-      <c r="B78" t="str">
-        <v>acceleration</v>
-      </c>
-      <c r="C78" t="str">
         <v>加速</v>
-      </c>
-      <c r="D78" t="str">
-        <v>acceleration(加速)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D78"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D45"/>
   </ignoredErrors>
 </worksheet>
 </file>